--- a/AAII_Financials/Yearly/SPIIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPIIY_YR_FIN.xlsx
@@ -741,10 +741,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>11183600</v>
+        <v>11194100</v>
       </c>
       <c r="E9" s="3">
-        <v>9405800</v>
+        <v>9421000</v>
       </c>
       <c r="F9" s="3">
         <v>8852800</v>
@@ -771,10 +771,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1135300</v>
+        <v>1124800</v>
       </c>
       <c r="E10" s="3">
-        <v>956900</v>
+        <v>941800</v>
       </c>
       <c r="F10" s="3">
         <v>889900</v>
@@ -875,10 +875,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>139600</v>
+        <v>139800</v>
       </c>
       <c r="E14" s="3">
-        <v>124000</v>
+        <v>108900</v>
       </c>
       <c r="F14" s="3">
         <v>112600</v>
@@ -946,10 +946,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11499800</v>
+        <v>11499600</v>
       </c>
       <c r="E17" s="3">
-        <v>9691400</v>
+        <v>9706500</v>
       </c>
       <c r="F17" s="3">
         <v>9145000</v>
@@ -976,10 +976,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>819100</v>
+        <v>819300</v>
       </c>
       <c r="E18" s="3">
-        <v>671400</v>
+        <v>656300</v>
       </c>
       <c r="F18" s="3">
         <v>597700</v>
@@ -1020,7 +1020,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>229300</v>
+        <v>229500</v>
       </c>
       <c r="E20" s="3">
         <v>28200</v>
@@ -1053,7 +1053,7 @@
         <v>812500</v>
       </c>
       <c r="E21" s="3">
-        <v>837300</v>
+        <v>822100</v>
       </c>
       <c r="F21" s="3">
         <v>742600</v>
@@ -1380,7 +1380,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-229300</v>
+        <v>-229500</v>
       </c>
       <c r="E32" s="3">
         <v>-28200</v>
@@ -1593,10 +1593,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>446400</v>
+        <v>446500</v>
       </c>
       <c r="E45" s="3">
-        <v>447400</v>
+        <v>449300</v>
       </c>
       <c r="F45" s="3">
         <v>443100</v>
@@ -1743,10 +1743,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>100600</v>
+        <v>108600</v>
       </c>
       <c r="E47" s="3">
-        <v>28700</v>
+        <v>35900</v>
       </c>
       <c r="F47" s="3">
         <v>21400</v>
@@ -1893,10 +1893,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>19700</v>
+        <v>11700</v>
       </c>
       <c r="E52" s="3">
-        <v>16600</v>
+        <v>9300</v>
       </c>
       <c r="F52" s="3">
         <v>10700</v>
